--- a/survey_templates/037_leadership_transformation_impact_survey--survey_templates.xlsx
+++ b/survey_templates/037_leadership_transformation_impact_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>leadership_development</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leadership Development</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>training_programs_choices</t>
+          <t>training_method_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Face-to-Face</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Face-to-Face</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>virtual</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>in-person</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>In-person</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>training_method_choices</t>
+          <t>training_participation_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>highly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Highly</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>highly</t>
+          <t>moderately</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Highly</t>
+          <t>Moderately</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>moderately</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Moderately</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>training_participation_choices</t>
+          <t>impact_on_performance_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>increased_productivity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Increased productivity</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>increased_productivity</t>
+          <t>improved_time_management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Increased productivity</t>
+          <t>Improved time management</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>improved_time_management</t>
+          <t>enhanced_leadership_skills</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Improved time management</t>
+          <t>Enhanced leadership skills</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>enhanced_leadership_skills</t>
+          <t>better_relationships_with_team_members</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Enhanced leadership skills</t>
+          <t>Better relationships with team members</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>better_relationships_with_team_members</t>
+          <t>improved_communication</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Better relationships with team members</t>
+          <t>Improved communication</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>impact_on_performance_choices</t>
+          <t>impact_on_engagement_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>improved_communication</t>
+          <t>increased_job_satisfaction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Improved communication</t>
+          <t>Increased job satisfaction</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>increased_job_satisfaction</t>
+          <t>improved_work-life_balance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Increased job satisfaction</t>
+          <t>Improved work-life balance</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>improved_work-life_balance</t>
+          <t>better_relationships_with_team_members</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Improved work-life balance</t>
+          <t>Better relationships with team members</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>better_relationships_with_team_members</t>
+          <t>improved_communication</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Better relationships with team members</t>
+          <t>Improved communication</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>improved_communication</t>
+          <t>enhanced_sense_of_purpose</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Improved communication</t>
+          <t>Enhanced sense of purpose</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>impact_on_engagement_choices</t>
+          <t>impact_on_job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>enhanced_sense_of_purpose</t>
+          <t>increased_job_satisfaction</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enhanced sense of purpose</t>
+          <t>Increased job satisfaction</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>increased_job_satisfaction</t>
+          <t>improved_work-life_balance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Increased job satisfaction</t>
+          <t>Improved work-life balance</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>improved_work-life_balance</t>
+          <t>better_relationships_with_team_members</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Improved work-life balance</t>
+          <t>Better relationships with team members</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>better_relationships_with_team_members</t>
+          <t>improved_communication</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Better relationships with team members</t>
+          <t>Improved communication</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>improved_communication</t>
+          <t>enhanced_sense_of_purpose</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Improved communication</t>
+          <t>Enhanced sense of purpose</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>impact_on_job_satisfaction_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>enhanced_sense_of_purpose</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Enhanced sense of purpose</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>semi-annual</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-annual</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>semi-annual</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Semi-annual</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>training_frequency_choices</t>
+          <t>training_focus_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>leadership_development</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Leadership development</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>leadership_development</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Leadership development</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
@@ -1726,78 +1726,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>project_management</t>
+          <t>team_building</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Team Building</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>training_focus_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>team_building</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Team Building</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>training_focus_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>leadership_development</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
-        <is>
-          <t>Leadership development</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
         <is>
           <t>False</t>
         </is>
